--- a/template.xlsx
+++ b/template.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="桶川店" sheetId="25" r:id="R386f85a28ed14a26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="平塚店" sheetId="31" r:id="Rcc34ca004f1b4c9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ふじみ野店" sheetId="30" r:id="R3179cb6e7ce040da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="鶴瀬店" sheetId="29" r:id="R84beba3210044a2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="美女木店" sheetId="28" r:id="R1787b75839a44bdd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="岩槻本店" sheetId="27" r:id="R3ec1dfa392f64310"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本部用" sheetId="15" r:id="R671edc1bb7534a2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="結果資料" sheetId="21" r:id="R55aaa4296b694496"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="桶川店" sheetId="25" r:id="R6413d696d8464c57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="平塚店" sheetId="31" r:id="R55ed991a44bb45ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ふじみ野店" sheetId="30" r:id="R9788e6f4b96342fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="鶴瀬店" sheetId="29" r:id="R3ef6ad871459402d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="美女木店" sheetId="28" r:id="R8f86d681a6734cc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="岩槻本店" sheetId="27" r:id="R059c2bbb2ce24bcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本部用" sheetId="15" r:id="R4788d27864f445df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="結果資料" sheetId="21" r:id="R30fd496f12c2492c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4784,7 +4784,7 @@
     <x:xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="1319">
+  <x:cellXfs count="898">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -7307,1185 +7307,6 @@
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="59" fillId="16" borderId="180" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="35" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="88" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="93" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="100" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="80" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="101" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="28" fillId="7" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="45" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="95" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="24" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="9" fontId="3" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="3" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="26" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="26" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="9" fontId="26" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="176" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="176" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="98" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="28" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="39" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="53" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="54" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="55" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="50" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="50" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="50" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="50" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="50" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="35" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="35" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="57" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="57" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="58" fillId="12" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="58" fillId="12" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="39" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="12" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="58" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="58" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="58" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="58" fillId="11" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="55" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="105" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="106" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="48" fillId="0" borderId="107" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="54" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="50" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="50" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="50" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="90" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="34" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="34" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="49" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="37" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="37" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="37" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="36" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="26" fillId="3" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="26" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="26" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="41" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="41" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="41" fillId="0" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="41" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="32" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="32" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="32" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="32" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="43" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="43" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="43" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="43" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="44" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="44" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="44" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="44" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="41" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="41" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="41" fillId="0" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="41" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="41" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="32" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="32" fillId="0" borderId="103" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="95" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="43" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="43" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="43" fillId="0" borderId="102" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="43" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="43" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="95" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="96" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="97" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="98" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="90" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="104" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="93" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="99" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="93" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="9" fontId="23" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="9" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="9" fontId="52" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="9" fontId="52" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="58" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="60" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="58" fillId="3" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="60" fillId="3" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="58" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="60" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -11297,7 +10118,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12b642725bcb4e47"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R384cd97c055d4aaa"/>
 </x:worksheet>
 </file>
 
@@ -13878,7 +12699,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec23b5c51547498f"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a73f046e6a04ba6"/>
 </x:worksheet>
 </file>
 
@@ -16459,7 +15280,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf923027ac2b343e7"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b18740cc2bf41ff"/>
 </x:worksheet>
 </file>
 
@@ -19040,7 +17861,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1253125c4d1246d5"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88f460eb988b4588"/>
 </x:worksheet>
 </file>
 
@@ -21621,7 +20442,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R602b419288c84226"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bbeea65ccfa4e16"/>
 </x:worksheet>
 </file>
 
@@ -24202,7 +23023,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75ab36498bf942b4"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdee3068afb914adb"/>
 </x:worksheet>
 </file>
 
@@ -26304,11 +25125,11 @@
       <x:c r="K7" s="279"/>
       <x:c r="L7" s="279"/>
       <x:c r="M7" s="279"/>
-      <x:c r="N7" s="1110" t="n">
+      <x:c r="N7" s="224" t="n">
         <x:f>AVERAGE(B7:G7)</x:f>
         <x:v>196.75</x:v>
       </x:c>
-      <x:c r="O7" s="1110" t="e">
+      <x:c r="O7" s="224" t="e">
         <x:f t="shared" ref="O7:O13" si="0">AVERAGE(H7:M7)</x:f>
         <x:v>#DIV/0!</x:v>
       </x:c>
@@ -26338,12 +25159,12 @@
       <x:c r="K8" s="279"/>
       <x:c r="L8" s="279"/>
       <x:c r="M8" s="279"/>
-      <x:c r="N8" s="1110" t="n">
-        <x:f>AVERAGE(B8:G8)</x:f>
+      <x:c r="N8" s="224" t="n">
+        <x:f>AVERAGE(B8:H8)</x:f>
         <x:v>195.5</x:v>
       </x:c>
-      <x:c r="O8" s="1110" t="e">
-        <x:f t="shared" si="0">AVERAGE(H8:M8)</x:f>
+      <x:c r="O8" s="224" t="e">
+        <x:f t="shared" si="0"/>
         <x:v>#DIV/0!</x:v>
       </x:c>
       <x:c r="P8" s="223"/>
@@ -26372,12 +25193,12 @@
       <x:c r="K9" s="279"/>
       <x:c r="L9" s="279"/>
       <x:c r="M9" s="279"/>
-      <x:c r="N9" s="1110" t="n">
-        <x:f>AVERAGE(B9:G9)</x:f>
+      <x:c r="N9" s="224" t="n">
+        <x:f>AVERAGE(B9:I9)</x:f>
         <x:v>197.25</x:v>
       </x:c>
-      <x:c r="O9" s="1110" t="e">
-        <x:f t="shared" si="0">AVERAGE(H9:M9)</x:f>
+      <x:c r="O9" s="224" t="e">
+        <x:f t="shared" si="0"/>
         <x:v>#DIV/0!</x:v>
       </x:c>
       <x:c r="P9" s="223"/>
@@ -26406,12 +25227,12 @@
       <x:c r="K10" s="279"/>
       <x:c r="L10" s="279"/>
       <x:c r="M10" s="279"/>
-      <x:c r="N10" s="1110" t="n">
+      <x:c r="N10" s="224" t="n">
         <x:f>AVERAGE(B10:G10)</x:f>
         <x:v>198.25</x:v>
       </x:c>
-      <x:c r="O10" s="1110" t="e">
-        <x:f t="shared" si="0">AVERAGE(H10:M10)</x:f>
+      <x:c r="O10" s="224" t="e">
+        <x:f t="shared" si="0"/>
         <x:v>#DIV/0!</x:v>
       </x:c>
       <x:c r="P10" s="223"/>
@@ -26440,12 +25261,12 @@
       <x:c r="K11" s="279"/>
       <x:c r="L11" s="279"/>
       <x:c r="M11" s="279"/>
-      <x:c r="N11" s="1110" t="n">
-        <x:f>AVERAGE(B11:G11)</x:f>
+      <x:c r="N11" s="224" t="n">
+        <x:f>AVERAGE(B11:I11)</x:f>
         <x:v>197.5</x:v>
       </x:c>
-      <x:c r="O11" s="1110" t="e">
-        <x:f t="shared" si="0">AVERAGE(H11:M11)</x:f>
+      <x:c r="O11" s="224" t="e">
+        <x:f t="shared" si="0"/>
         <x:v>#DIV/0!</x:v>
       </x:c>
       <x:c r="P11" s="223"/>
@@ -26474,12 +25295,12 @@
       <x:c r="K12" s="278"/>
       <x:c r="L12" s="278"/>
       <x:c r="M12" s="278"/>
-      <x:c r="N12" s="1110" t="n">
+      <x:c r="N12" s="224" t="n">
         <x:f>AVERAGE(B12:G12)</x:f>
         <x:v>197.5</x:v>
       </x:c>
-      <x:c r="O12" s="1110" t="e">
-        <x:f t="shared" si="0">AVERAGE(H12:M12)</x:f>
+      <x:c r="O12" s="224" t="e">
+        <x:f t="shared" si="0"/>
         <x:v>#DIV/0!</x:v>
       </x:c>
       <x:c r="P12" s="223"/>
@@ -26508,12 +25329,12 @@
       <x:c r="K13" s="280"/>
       <x:c r="L13" s="280"/>
       <x:c r="M13" s="280"/>
-      <x:c r="N13" s="1110" t="n">
-        <x:f>AVERAGE(B13:G13)</x:f>
+      <x:c r="N13" s="224" t="n">
+        <x:f>AVERAGE(B13:H13)</x:f>
         <x:v>96.25</x:v>
       </x:c>
-      <x:c r="O13" s="1110" t="e">
-        <x:f t="shared" si="0">AVERAGE(H13:M13)</x:f>
+      <x:c r="O13" s="224" t="e">
+        <x:f t="shared" si="0"/>
         <x:v>#DIV/0!</x:v>
       </x:c>
       <x:c r="P13" s="223"/>
@@ -26672,7 +25493,7 @@
       <x:c r="K20" s="279"/>
       <x:c r="L20" s="279"/>
       <x:c r="M20" s="279"/>
-      <x:c r="N20" s="1113" t="n">
+      <x:c r="N20" s="228" t="n">
         <x:f t="shared" ref="N20:N25" si="1">AVERAGE(B20:M20)</x:f>
         <x:v>3.25</x:v>
       </x:c>
@@ -26701,9 +25522,9 @@
       <x:c r="K21" s="279"/>
       <x:c r="L21" s="279"/>
       <x:c r="M21" s="279"/>
-      <x:c r="N21" s="1113" t="n">
-        <x:f t="shared" si="1">AVERAGE(B21:M21)</x:f>
-        <x:v>3.75</x:v>
+      <x:c r="N21" s="228">
+        <x:f t="shared" si="1"/>
+        <x:v>3.5</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="26.25" customHeight="1">
@@ -26730,9 +25551,9 @@
       <x:c r="K22" s="279"/>
       <x:c r="L22" s="279"/>
       <x:c r="M22" s="279"/>
-      <x:c r="N22" s="1110" t="n">
-        <x:f t="shared" si="1">AVERAGE(B22:M22)</x:f>
-        <x:v>2.25</x:v>
+      <x:c r="N22" s="224">
+        <x:f t="shared" si="1"/>
+        <x:v>1.5</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="26.25" customHeight="1">
@@ -26759,8 +25580,8 @@
       <x:c r="K23" s="279"/>
       <x:c r="L23" s="279"/>
       <x:c r="M23" s="279"/>
-      <x:c r="N23" s="1110" t="n">
-        <x:f t="shared" si="1">AVERAGE(B23:M23)</x:f>
+      <x:c r="N23" s="224">
+        <x:f t="shared" si="1"/>
         <x:v>1.5</x:v>
       </x:c>
     </x:row>
@@ -26788,9 +25609,9 @@
       <x:c r="K24" s="279"/>
       <x:c r="L24" s="279"/>
       <x:c r="M24" s="279"/>
-      <x:c r="N24" s="1110" t="n">
-        <x:f t="shared" si="1">AVERAGE(B24:M24)</x:f>
-        <x:v>2.5</x:v>
+      <x:c r="N24" s="224">
+        <x:f t="shared" si="1"/>
+        <x:v>1.5</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26.25" customHeight="1">
@@ -26817,9 +25638,9 @@
       <x:c r="K25" s="279"/>
       <x:c r="L25" s="279"/>
       <x:c r="M25" s="279"/>
-      <x:c r="N25" s="1110" t="n">
-        <x:f t="shared" si="1">AVERAGE(B25:M25)</x:f>
-        <x:v>2.75</x:v>
+      <x:c r="N25" s="224">
+        <x:f t="shared" si="1"/>
+        <x:v>3.5</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="14.399999618530273">
@@ -27007,6 +25828,6 @@
     <x:mergeCell ref="F36:G36"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf81bb3b93b204216"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf941c1a61f3b4d3a"/>
 </x:worksheet>
 </file>